--- a/docs/malzeme_listesi.xlsx
+++ b/docs/malzeme_listesi.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,6 +43,16 @@
     <font>
       <b val="1"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00808080"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
@@ -148,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -187,11 +197,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -561,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -671,7 +685,7 @@
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
-          <t>Döngüde ~21 boru ucu var. 20 yetersiz, yedekle 30.</t>
+          <t>Döngüde 21 boru ucu var. 20 yedeksiz kalıyordu, 30'a çıkarıldı.</t>
         </is>
       </c>
     </row>
@@ -709,7 +723,7 @@
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>Her sökümde yenilenir. 20'den 30'a çıkarıldı.</t>
+          <t>Her sökümde yenilenir. 20'den 30'a.</t>
         </is>
       </c>
     </row>
@@ -747,7 +761,7 @@
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>PTFE hortum için ZORUNLU. Her boru ucuna bir tane. 20'den 30'a.</t>
+          <t>PTFE hortum için ZORUNLU, her boru ucuna bir tane. 20'den 30'a.</t>
         </is>
       </c>
     </row>
@@ -790,40 +804,40 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>BAĞLANTI</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>CMC 6M-2G-S316</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>Male connector, 6 mm tube x G1/8 BSPP erkek</t>
         </is>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="9" t="n"/>
-      <c r="G7" s="9">
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6">
         <f>IF(F7="","",E7*F7)</f>
         <v/>
       </c>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>Neumo (Hy-Lok)</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>KNF pompa portları. BONDED WASHER'lı istenecek, PTFE bant işe yaramaz.</t>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>ŞARTLI: N 86'nın portu G1/8 idi. Pompa modeli değiştiği için port tipi teyit edilip bu kalem güncellenecek. Bonded washer'lı istenecek.</t>
         </is>
       </c>
     </row>
@@ -923,7 +937,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6">
@@ -937,7 +951,7 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>1) PCD kör dalı 2) pompa bypass hattı 3) süpürme portu. 1'den 3'e.</t>
+          <t>1) PCD kör dalı 2) süpürme portu. Bypass iptal olduğu için 3'ten 2'ye indi.</t>
         </is>
       </c>
     </row>
@@ -975,7 +989,7 @@
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
-          <t>CMC 6M-2G için yedek conta.</t>
+          <t>CMC 6M-2G için yedek conta. Port tipi değişirse bu da değişir.</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1027,7 @@
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
-          <t>YENİ. ADM'yi partikül kirlenmesinden korur. Odacık çıkışına, PCD'den önce. Sinterlenmiş SS tercih; membran daha çok yüzey demek.</t>
+          <t>YENİ. ADM'yi partikül kirlenmesinden korur. Odacık çıkışına, PCD'den önce. Sinterlenmiş SS tercih edildi: inert ve yüzey alanı düşük.</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1047,7 @@
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>İğne vana, 6 mm sıkıştırmalı</t>
+          <t>Kapama vanası, 6 mm sıkıştırmalı</t>
         </is>
       </c>
       <c r="E13" s="11" t="n">
@@ -1051,45 +1065,45 @@
       </c>
       <c r="I13" s="13" t="inlineStr">
         <is>
-          <t>YENİ. Pompa bypass hattında, ana döngü debisini ayarlar. Mevcut iğne vana varsa alınmaz.</t>
+          <t>YENİ. Süpürme (purge) portu. Deneyler arası N2 ile hattı temizlemek için. Ölçüm sırasında kapalı.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n">
+      <c r="A14" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>BAĞLANTI</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>— (kod istenecek)</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>Kapama vanası, 6 mm sıkıştırmalı</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="n">
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>PTFE thread sealant (bant veya pasta)</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="12" t="n"/>
-      <c r="G14" s="12">
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="9">
         <f>IF(F14="","",E14*F14)</f>
         <v/>
       </c>
-      <c r="H14" s="12" t="inlineStr">
-        <is>
-          <t>Neumo (Hy-Lok)</t>
-        </is>
-      </c>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>YENİ. Süpürme (purge) portu. Deneyler arası N2 ile hattı temizlemek için.</t>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>Neumo / hırdavat</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>NPT dişleri için. İlk 1-2 diş boş bırakılır.</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1123,7 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>PTFE thread sealant (bant veya pasta)</t>
+          <t>Tube cutter, 6 mm</t>
         </is>
       </c>
       <c r="E15" s="8" t="n">
@@ -1127,7 +1141,7 @@
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
-          <t>NPT dişleri için. İlk 1-2 diş boş bırakılır.</t>
+          <t>Dik kesim şart. Falçata ferrule'ü sızdırtır.</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1161,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>Tube cutter, 6 mm</t>
+          <t>Kaçak arama sıvısı (Snoop vb.)</t>
         </is>
       </c>
       <c r="E16" s="8" t="n">
@@ -1165,7 +1179,7 @@
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>Dik kesim şart. Falçata ferrule'ü sızdırtır.</t>
+          <t>Sabunlu su da olur.</t>
         </is>
       </c>
     </row>
@@ -1185,11 +1199,11 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>Kaçak arama sıvısı (Snoop vb.)</t>
+          <t>Açık ağız anahtar, 14 mm ve 15 mm</t>
         </is>
       </c>
       <c r="E17" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="9" t="n"/>
       <c r="G17" s="9">
@@ -1198,143 +1212,120 @@
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>Neumo / hırdavat</t>
+          <t>Hırdavat</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>Sabunlu su da olur.</t>
+          <t>Gövdeyi tutup somunu sıkmak için ikisi birden gerekli.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>BAĞLANTI</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>POMPA / AKIŞ</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+      <c r="I18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>POMPA / AKIŞ</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>KNF NMP830 KTDC-B</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>Mikro diyafram pompa, 2,1 L/dk, fırçasız DC, devir ayarlı</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="12" t="n"/>
+      <c r="G19" s="12">
+        <f>IF(F19="","",E19*F19)</f>
+        <v/>
+      </c>
+      <c r="H19" s="12" t="inlineStr">
+        <is>
+          <t>KNF Türkiye</t>
+        </is>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>N 86 KT.18 (5,5 L/dk, 230 V AC) yerine. Fırçasız DC olduğu için devir voltaj/PWM ile düşürülür, bypass gerekmez. SİPARİŞTE BELİRT: PPS başlık + PTFE kaplı diyafram + FFKM valf (CR/EPDM olmaz). Port tipi teyit edilecek.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>POMPA / AKIŞ</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Alicat 200 sccm MFC</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>Döngü debi kontrol + ölçüm (ELİMİZDE VAR)</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="12" t="n"/>
+      <c r="G20" s="12">
+        <f>IF(F20="","",E20*F20)</f>
+        <v/>
+      </c>
+      <c r="H20" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>Açık ağız anahtar, 14 mm ve 15 mm</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F18" s="9" t="n"/>
-      <c r="G18" s="9">
-        <f>IF(F18="","",E18*F18)</f>
-        <v/>
-      </c>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>Hırdavat</t>
-        </is>
-      </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>Gövdeyi tutup somunu sıkmak için ikisi birden gerekli.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>POMPA / AKIŞ</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="4" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>POMPA / AKIŞ</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>KNF N 86 KT.18</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>Diyafram pompa, 230 V / 50 Hz, 5,5 L/dk, G1/8 port</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6">
-        <f>IF(F20="","",E20*F20)</f>
-        <v/>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>KNF Türkiye</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>Islak malzemeler ideal: PPS başlık + PTFE kaplı diyafram + FFPM valf. ANCAK 5,5 L/dk hedefimizin ~25 katı. Çözüm: pompa etrafına bypass (üstteki tee + iğne vana). Pompa tam devirde çalışır, ısınmaz; ana döngüye istediğimiz debi gider.</t>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>Kontrol modunda 150-200 sccm set edilir: hem debiyi belirler hem ölçer. Ayrı rotametreye gerek yok. Gaz seçimi 'Air'. Pompa çıkışı ile odacık girişi arasına.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>POMPA / AKIŞ</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>KNF NMP830 KTDC-B</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>ALTERNATİF: mikro diyafram pompa, 2,1 L/dk, fırçasız DC</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="12" t="n"/>
-      <c r="G21" s="12">
-        <f>IF(F21="","",E21*F21)</f>
-        <v/>
-      </c>
-      <c r="H21" s="12" t="inlineStr">
-        <is>
-          <t>KNF Türkiye</t>
-        </is>
-      </c>
-      <c r="I21" s="13" t="inlineStr">
-        <is>
-          <t>Henüz sipariş verilmediyse bunu değerlendir. Fırçasız DC olduğu için devir voltajla ayarlanır, bypass gerekmez. SORULACAK: valf malzemesi FKM veya FFKM olmalı, CR (kloropren) olmaz.</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>ODACIK</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="n">
@@ -1342,21 +1333,21 @@
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>POMPA / AKIŞ</t>
+          <t>ODACIK</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>Alicat 200 sccm MFC</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>Döngü debi ölçer (ELİMİZDE VAR)</t>
+          <t>PTFE hortum, 6 mm dış / 4 mm iç çap</t>
         </is>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F22" s="12" t="n"/>
       <c r="G22" s="12">
@@ -1365,67 +1356,90 @@
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
+          <t>Neumo / lab sarf</t>
+        </is>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>YENİ. Önceki listede insert vardı ama hortumun kendisi yoktu. Birim: metre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>ODACIK</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I22" s="13" t="inlineStr">
-        <is>
-          <t>Vana tam açık, gaz seçimi 'Air'. Hedef debi 150-200 sccm. Ayrı rotametreye gerek kalmaz.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>POMPA / AKIŞ</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Dwyer RMA-2-SSV-VIT vb.</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>OPSİYONEL rotametre + iğne vana, 0,1-1 L/dk hava</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="n">
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>Cam kavanoz, 1 L borosilikat, geniş ağız, PTFE astarlı kapak</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F23" s="6" t="n"/>
-      <c r="G23" s="6">
+      <c r="F23" s="12" t="n"/>
+      <c r="G23" s="12">
         <f>IF(F23="","",E23*F23)</f>
         <v/>
       </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>ITM / Tetisan</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>DİKKAT: önceki listedeki RMA-21 modeli 1-10 L/dk. Bizim çalışma debimiz 0,15-0,5 L/dk, o skalanın en altında okunmaz. Alınacaksa düşük skalalı model alınmalı.</t>
+      <c r="H23" s="12" t="inlineStr">
+        <is>
+          <t>Lab sarf</t>
+        </is>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>YENİ. Gazın biriktiği hacim burası. 30 L kutuda derişim 30 kat düşer.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>ODACIK</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="n"/>
-      <c r="G24" s="3" t="n"/>
-      <c r="H24" s="3" t="n"/>
-      <c r="I24" s="4" t="n"/>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>O-ring, Viton (FKM), ~11 mm iç çap x 2 mm kesit</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" s="9" t="n"/>
+      <c r="G24" s="9">
+        <f>IF(F24="","",E24*F24)</f>
+        <v/>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>Conta/hidrolik</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Bulkhead union'ın duvara sızdırmazlığı. Karışık ölçü seti pratik.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="n">
@@ -1443,11 +1457,11 @@
       </c>
       <c r="D25" s="13" t="inlineStr">
         <is>
-          <t>PTFE hortum, 6 mm dış / 4 mm iç çap</t>
+          <t>Silikon conta bandı, kutu kapağı için</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F25" s="12" t="n"/>
       <c r="G25" s="12">
@@ -1456,12 +1470,12 @@
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>Neumo / lab sarf</t>
+          <t>Hırdavat</t>
         </is>
       </c>
       <c r="I25" s="13" t="inlineStr">
         <is>
-          <t>YENİ. Önceki listede insert vardı ama hortumun kendisi yoktu. Birim: metre.</t>
+          <t>YENİ. Birim: metre.</t>
         </is>
       </c>
     </row>
@@ -1476,12 +1490,12 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SHT31 veya muadili</t>
         </is>
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>Cam kavanoz, 1 L borosilikat, geniş ağız, PTFE astarlı kapak</t>
+          <t>Sıcaklık / bağıl nem sensörü, kayıtlı</t>
         </is>
       </c>
       <c r="E26" s="11" t="n">
@@ -1494,90 +1508,67 @@
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
+          <t>Elektronik</t>
+        </is>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>YENİ. Kapalı döngüde nem dengeye gelir, bunu kayıtla kanıtlamak gerekiyor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>ODACIK</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>Nitril eldiven + kelepçe (kutuya eldiven portu)</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12">
+        <f>IF(F27="","",E27*F27)</f>
+        <v/>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
           <t>Lab sarf</t>
         </is>
       </c>
-      <c r="I26" s="13" t="inlineStr">
-        <is>
-          <t>YENİ. Gazın biriktiği hacim burası. 30 L kutuda derişim 30 kat düşer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>ODACIK</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>O-ring, Viton (FKM), ~11 mm iç çap x 2 mm kesit</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F27" s="9" t="n"/>
-      <c r="G27" s="9">
-        <f>IF(F27="","",E27*F27)</f>
-        <v/>
-      </c>
-      <c r="H27" s="9" t="inlineStr">
-        <is>
-          <t>Conta/hidrolik</t>
-        </is>
-      </c>
-      <c r="I27" s="10" t="inlineStr">
-        <is>
-          <t>Bulkhead union'ın duvara sızdırmazlığı. Karışık ölçü seti pratik.</t>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>YENİ. Kapağı açmadan kesim yapmak için. Birim: takım.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>ODACIK</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D28" s="13" t="inlineStr">
-        <is>
-          <t>Silikon conta bandı, kutu kapağı için</t>
-        </is>
-      </c>
-      <c r="E28" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="12" t="n"/>
-      <c r="G28" s="12">
-        <f>IF(F28="","",E28*F28)</f>
-        <v/>
-      </c>
-      <c r="H28" s="12" t="inlineStr">
-        <is>
-          <t>Hırdavat</t>
-        </is>
-      </c>
-      <c r="I28" s="13" t="inlineStr">
-        <is>
-          <t>YENİ. Birim: metre.</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>TEST BİLEŞİĞİ</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="3" t="n"/>
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+      <c r="I28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="n">
@@ -1585,17 +1576,17 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>ODACIK</t>
+          <t>TEST BİLEŞİĞİ</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>SHT31 veya muadili</t>
+          <t>CAS 119-36-8</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>Sıcaklık / bağıl nem sensörü, kayıtlı</t>
+          <t>Metil salisilat, reaktif saflığı &gt;=%99, 100 mL</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
@@ -1608,12 +1599,12 @@
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>Elektronik</t>
+          <t>Merck / Sigma / Isolab</t>
         </is>
       </c>
       <c r="I29" s="13" t="inlineStr">
         <is>
-          <t>YENİ. Nem kaymasını kayıt altına almak için. Kapalı döngüde nem dengeye gelir ama kanıtlanmalı.</t>
+          <t>YENİ. PoC test bileşiği. Kış yeşili yağı ALINMAYACAK, o bir karışım. OSHA maruziyet sınırı yok, parlama noktası &gt;110 C, FEMA GRAS.</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1614,7 @@
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>ODACIK</t>
+          <t>TEST BİLEŞİĞİ</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
@@ -1633,11 +1624,11 @@
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>Nitril eldiven + kelepçe (kutuya eldiven portu)</t>
+          <t>Mikrolitre şırınga, 10 µL, gaz sızdırmaz</t>
         </is>
       </c>
       <c r="E30" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30" s="12" t="n"/>
       <c r="G30" s="12">
@@ -1651,223 +1642,163 @@
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
-          <t>YENİ. Kapağı açmadan kesim yapmak için. Birim: takım.</t>
+          <t>YENİ. Tek doz 0,2-1 µL. 1 L kavanozda 0,2 µL yaklaşık 27 ppm eder.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TEST BİLEŞİĞİ</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="n"/>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="n"/>
-      <c r="G31" s="3" t="n"/>
-      <c r="H31" s="3" t="n"/>
-      <c r="I31" s="4" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="12" t="inlineStr">
-        <is>
-          <t>TEST BİLEŞİĞİ</t>
-        </is>
-      </c>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
-          <t>CAS 119-36-8</t>
-        </is>
-      </c>
-      <c r="D32" s="13" t="inlineStr">
-        <is>
-          <t>Metil salisilat, reaktif saflığı &gt;=%99, 100 mL</t>
-        </is>
-      </c>
-      <c r="E32" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="12" t="n"/>
-      <c r="G32" s="12">
-        <f>IF(F32="","",E32*F32)</f>
-        <v/>
-      </c>
-      <c r="H32" s="12" t="inlineStr">
-        <is>
-          <t>Merck / Sigma / Isolab</t>
-        </is>
-      </c>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>YENİ. PoC test bileşiği. Kış yeşili yağı ALINMAYACAK, o bir karışım. OSHA maruziyet sınırı yok, parlama noktası &gt;110 C, FEMA GRAS.</t>
-        </is>
-      </c>
+      <c r="A31" s="14" t="n"/>
+      <c r="B31" s="14" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>TOPLAM</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="15">
+        <f>SUM(G2:G30)</f>
+        <v/>
+      </c>
+      <c r="H31" s="14" t="n"/>
+      <c r="I31" s="14" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>TEST BİLEŞİĞİ</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D33" s="13" t="inlineStr">
-        <is>
-          <t>Mikrolitre şırınga, 10 µL, gaz sızdırmaz</t>
-        </is>
-      </c>
-      <c r="E33" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="12" t="n"/>
-      <c r="G33" s="12">
-        <f>IF(F33="","",E33*F33)</f>
-        <v/>
-      </c>
-      <c r="H33" s="12" t="inlineStr">
-        <is>
-          <t>Lab sarf</t>
-        </is>
-      </c>
-      <c r="I33" s="13" t="inlineStr">
-        <is>
-          <t>YENİ. Tek doz 0,2-1 µL. 1 L kavanozda 0,2 µL ~ 27 ppm.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="14" t="n"/>
-      <c r="B34" s="14" t="n"/>
-      <c r="C34" s="14" t="n"/>
-      <c r="D34" s="15" t="inlineStr">
-        <is>
-          <t>TOPLAM</t>
-        </is>
-      </c>
-      <c r="E34" s="14" t="n"/>
-      <c r="F34" s="14" t="n"/>
-      <c r="G34" s="15">
-        <f>SUM(G2:G33)</f>
-        <v/>
-      </c>
-      <c r="H34" s="14" t="n"/>
-      <c r="I34" s="14" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t>LEJANT</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="17" t="inlineStr">
-        <is>
-          <t>Sarı = yeni eklendi</t>
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>İPTAL EDİLENLER</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>KNF N 86 KT.18 (5,5 L/dk, 230 V AC) - debisi hedefin 25 katı ve sabit devir. Yerine NMP830 KTDC-B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>Dwyer RMA-21-SSV-VIT rotametre (1-10 L/dk) - hem skalası yanlıştı hem de MFC entegre edildiği için gereksiz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>Pompa bypass hattı (tee + iğne vana) - pompa debisi doğrudan düşürüleceği için gerekmiyor.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="18" t="inlineStr">
         <is>
-          <t>Turuncu = adet veya model değiştirildi</t>
+          <t>LEJANT</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="19" t="inlineStr">
         <is>
+          <t>Sarı = yeni eklendi</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="20" t="inlineStr">
+        <is>
+          <t>Turuncu = adet veya model değiştirildi</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="21" t="inlineStr">
+        <is>
           <t>Renksiz = önceki listeden aynen geldi</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="20" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="22" t="inlineStr">
         <is>
           <t>SİPARİŞ ÖNCESİ DOĞRULANACAKLAR</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="26" customHeight="1">
-      <c r="A42" s="21" t="inlineStr">
-        <is>
-          <t>1. ADM01'in gaz portu ölçüsü. Thorlabs ADM01 Hy-Lok rakorla geliyor ama 1/4" mi 6 mm mi fiziksel olarak ölçülmeli. Mevcut hatta zaten bağlı olduğu için oradaki rakorlar tekrar kullanılabilir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="21" t="inlineStr">
-        <is>
-          <t>2. Alicat MFC ve PCD port tipleri. Liste 1/8" NPT varsayıyor (PCD'de takılı olan '9A' damgalı connector bunu doğruluyor). MFC için cihazın üstünden teyit edilmeli.</t>
-        </is>
-      </c>
-    </row>
     <row r="44" ht="26" customHeight="1">
-      <c r="A44" s="21" t="inlineStr">
-        <is>
-          <t>3. Hy-Lok gövdeleri (tee, bulkhead, connector) somun+ferrule takılı mı geliyor? Genelde evet. Neumo'ya sorulmalı, yoksa somun/ferrule adedi artırılmalı.</t>
+      <c r="A44" s="23" t="inlineStr">
+        <is>
+          <t>1. ADM01'in gaz portu ölçüsü. Thorlabs ADM01 Hy-Lok rakorla geliyor ama 1/4" mi 6 mm mi katalogda yazmıyor. Mevcut hatta zaten bağlı, oradaki rakor ölçülerek teyit edilecek.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
-      <c r="A45" s="21" t="inlineStr">
-        <is>
-          <t>4. KNF NMP830 KTDC valf malzemesi. FKM veya FFKM olmalı; CR (kloropren) uçucuları emer.</t>
+      <c r="A45" s="23" t="inlineStr">
+        <is>
+          <t>2. NMP830'un port tipi (G1/8 diş mi, hortum nipeli mi). CMC 6M-2G kalemi buna göre güncellenecek.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="26" customHeight="1">
-      <c r="A46" s="21" t="inlineStr">
-        <is>
-          <t>5. Filtre ve vana kodları Neumo'dan istenecek. 6 mm sıkıştırmalı uçlu, 2 µm eleman.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="22" t="inlineStr">
+      <c r="A46" s="23" t="inlineStr">
+        <is>
+          <t>3. Alicat MFC ve PCD port tipleri. Liste 1/8" NPT varsayıyor; PCD'de takılı '9A' damgalı connector bunu doğruluyor, MFC cihazın üstünden teyit edilecek.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="23" t="inlineStr">
+        <is>
+          <t>4. Hy-Lok gövdeleri (tee, bulkhead, connector) somun+ferrule takılı mı geliyor? Genelde evet; değilse somun/ferrule adedi artırılacak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="26" customHeight="1">
+      <c r="A48" s="23" t="inlineStr">
+        <is>
+          <t>5. Filtre ve kapama vanası kodları Neumo'dan istenecek: 6 mm sıkıştırmalı uçlu, filtre elemanı 2 µm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="24" t="inlineStr">
         <is>
           <t>DÖNGÜ SIRASI</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="19" t="inlineStr">
-        <is>
-          <t>Odacık çıkışı -&gt; Filtre -&gt; PCD (T ile kör dal) -&gt; ADM -&gt; Pompa -&gt; İğne vana (bypass) -&gt; MFC -&gt; Odacık girişi</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="26" customHeight="1">
-      <c r="A50" s="21" t="inlineStr">
-        <is>
-          <t>Kısma her zaman pompadan SONRA. Böylece ADM emme tarafında, odacık basıncında kalır; pompa çıkışı ile vana arası dışında hiçbir yerde basınç yükselmez.</t>
+    <row r="51" ht="26" customHeight="1">
+      <c r="A51" s="23" t="inlineStr">
+        <is>
+          <t>Odacık çıkışı -&gt; Filtre -&gt; PCD (T ile kör dal) -&gt; ADM -&gt; Pompa -&gt; MFC -&gt; Odacık girişi</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="A52" s="23" t="inlineStr">
+        <is>
+          <t>Debiyi pompanın devri kabaca, MFC ince olarak belirler. ADM pompanın emme tarafında kaldığı için odacık basıncında çalışır; hiçbir yerde basınç yükselmez. Hedef debi 150-200 sccm, 1 L kavanozu 5-7 dakikada çevirir.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A43:I43"/>
-    <mergeCell ref="A19:I19"/>
+  <mergeCells count="14">
+    <mergeCell ref="A52:I52"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A49:I49"/>
-    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A51:I51"/>
+    <mergeCell ref="A47:I47"/>
+    <mergeCell ref="A28:I28"/>
     <mergeCell ref="A46:I46"/>
+    <mergeCell ref="A36:I36"/>
     <mergeCell ref="A44:I44"/>
     <mergeCell ref="A45:I45"/>
-    <mergeCell ref="A31:I31"/>
-    <mergeCell ref="A50:I50"/>
-    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A48:I48"/>
+    <mergeCell ref="A21:I21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>

--- a/docs/malzeme_listesi.xlsx
+++ b/docs/malzeme_listesi.xlsx
@@ -158,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -210,6 +210,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1236,41 +1242,41 @@
       <c r="H18" s="3" t="n"/>
       <c r="I18" s="4" t="n"/>
     </row>
-    <row r="19">
-      <c r="A19" s="11" t="n">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="25" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>POMPA / AKIŞ</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>KNF NMP830 KTDC-B</t>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>KNF — model istenecek</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>Mikro diyafram pompa, 2,1 L/dk, fırçasız DC, devir ayarlı</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="n">
+          <t>Mikro diyafram pompa, çalışma debisi 150–300 sccm, fırçasız DC</t>
+        </is>
+      </c>
+      <c r="E19" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="12" t="n"/>
-      <c r="G19" s="12">
+      <c r="F19" s="26" t="n"/>
+      <c r="G19" s="26">
         <f>IF(F19="","",E19*F19)</f>
         <v/>
       </c>
-      <c r="H19" s="12" t="inlineStr">
+      <c r="H19" s="26" t="inlineStr">
         <is>
           <t>KNF Türkiye</t>
         </is>
       </c>
       <c r="I19" s="13" t="inlineStr">
         <is>
-          <t>N 86 KT.18 (5,5 L/dk, 230 V AC) yerine. Fırçasız DC olduğu için devir voltaj/PWM ile düşürülür, bypass gerekmez. SİPARİŞTE BELİRT: PPS başlık + PTFE kaplı diyafram + FFKM valf (CR/EPDM olmaz). Port tipi teyit edilecek.</t>
+          <t>ŞARTNAME KNF TÜRKİYE'YE VERİLECEK: 150–300 sccm çalışma debisi, PPS/PTFE ıslak yüzey, PTFE kaplı diyafram, FFKM valf, fırçasız DC (devir ayarlı). NMP 03 / NMP 05 serisi debi olarak uygun ama PTFE diyafram 'talep üzerine' — teyit edilecek. NMP830 KTDC-B'de PTFE+FFKM standart ama debisi 2100 sccm, yani hedefin 10 katı; son çare olarak devri kısılıp MFC ile kontrol edilerek kullanılabilir.</t>
         </is>
       </c>
     </row>
@@ -1664,6 +1670,7 @@
       <c r="H31" s="14" t="n"/>
       <c r="I31" s="14" t="n"/>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
         <is>
@@ -1692,6 +1699,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="18" t="inlineStr">
         <is>
@@ -1720,6 +1728,7 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="22" t="inlineStr">
         <is>
@@ -1730,14 +1739,14 @@
     <row r="44" ht="26" customHeight="1">
       <c r="A44" s="23" t="inlineStr">
         <is>
-          <t>1. ADM01'in gaz portu ölçüsü. Thorlabs ADM01 Hy-Lok rakorla geliyor ama 1/4" mi 6 mm mi katalogda yazmıyor. Mevcut hatta zaten bağlı, oradaki rakor ölçülerek teyit edilecek.</t>
+          <t>1. Rakor ölçüleri (6 mm) önceki siparişten teyitli — ADM01, PCD ve MFC hattı zaten bu ölçüde kurulu. PCD'de takılı '9A' damgalı connector 1/8" NPT'yi doğruluyor. Yeni doğrulama gerekmiyor.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
       <c r="A45" s="23" t="inlineStr">
         <is>
-          <t>2. NMP830'un port tipi (G1/8 diş mi, hortum nipeli mi). CMC 6M-2G kalemi buna göre güncellenecek.</t>
+          <t>2. Seçilecek pompanın port tipi (G1/8 diş mi, hortum nipeli mi). CMC 6M-2G kalemi buna göre güncellenecek.</t>
         </is>
       </c>
     </row>
@@ -1762,6 +1771,7 @@
         </is>
       </c>
     </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" s="24" t="inlineStr">
         <is>

--- a/docs/malzeme_listesi.xlsx
+++ b/docs/malzeme_listesi.xlsx
@@ -158,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -210,6 +210,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -733,7 +739,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="42" customHeight="1">
       <c r="A5" s="5" t="n">
         <v>4</v>
       </c>
@@ -767,7 +773,7 @@
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>PTFE hortum için ZORUNLU, her boru ucuna bir tane. 20'den 30'a.</t>
+          <t>PTFE hortum için ZORUNLU, her boru ucuna bir tane. 20'den 30'a. DİKKAT: 23.01.2026 teklifinde teslim süresi 4-5 HAFTA (somun ve ferrule stokta). Sipariş sırasında bu kalemi öne al. Birim fiyat ~1,42 EUR.</t>
         </is>
       </c>
     </row>
@@ -1000,15 +1006,15 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n">
+      <c r="A12" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>BAĞLANTI</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="26" t="inlineStr">
         <is>
           <t>— (kod istenecek)</t>
         </is>
@@ -1018,15 +1024,15 @@
           <t>Hat içi filtre, 6 mm sıkıştırmalı, 2 µm sinterlenmiş SS eleman</t>
         </is>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="12" t="n"/>
-      <c r="G12" s="12">
+      <c r="F12" s="26" t="n"/>
+      <c r="G12" s="26">
         <f>IF(F12="","",E12*F12)</f>
         <v/>
       </c>
-      <c r="H12" s="12" t="inlineStr">
+      <c r="H12" s="26" t="inlineStr">
         <is>
           <t>Neumo (Hy-Lok)</t>
         </is>
@@ -1038,15 +1044,15 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="n">
+      <c r="A13" s="25" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>BAĞLANTI</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="26" t="inlineStr">
         <is>
           <t>— (kod istenecek)</t>
         </is>
@@ -1056,15 +1062,15 @@
           <t>Kapama vanası, 6 mm sıkıştırmalı</t>
         </is>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12">
+      <c r="F13" s="26" t="n"/>
+      <c r="G13" s="26">
         <f>IF(F13="","",E13*F13)</f>
         <v/>
       </c>
-      <c r="H13" s="12" t="inlineStr">
+      <c r="H13" s="26" t="inlineStr">
         <is>
           <t>Neumo (Hy-Lok)</t>
         </is>
@@ -1242,18 +1248,18 @@
       <c r="H18" s="3" t="n"/>
       <c r="I18" s="4" t="n"/>
     </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="25" t="n">
+    <row r="19" ht="86" customHeight="1">
+      <c r="A19" s="27" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="26" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>POMPA / AKIŞ</t>
         </is>
       </c>
-      <c r="C19" s="26" t="inlineStr">
-        <is>
-          <t>KNF — model istenecek</t>
+      <c r="C19" s="28" t="inlineStr">
+        <is>
+          <t>Marka serbest — model istenecek</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
@@ -1261,35 +1267,35 @@
           <t>Mikro diyafram pompa, çalışma debisi 150–300 sccm, fırçasız DC</t>
         </is>
       </c>
-      <c r="E19" s="25" t="n">
+      <c r="E19" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="26" t="n"/>
-      <c r="G19" s="26">
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="28">
         <f>IF(F19="","",E19*F19)</f>
         <v/>
       </c>
-      <c r="H19" s="26" t="inlineStr">
-        <is>
-          <t>KNF Türkiye</t>
+      <c r="H19" s="28" t="inlineStr">
+        <is>
+          <t>Parker / Schwarzer / Thomas / KNF — teklif alınacak</t>
         </is>
       </c>
       <c r="I19" s="13" t="inlineStr">
         <is>
-          <t>ŞARTNAME KNF TÜRKİYE'YE VERİLECEK: 150–300 sccm çalışma debisi, PPS/PTFE ıslak yüzey, PTFE kaplı diyafram, FFKM valf, fırçasız DC (devir ayarlı). NMP 03 / NMP 05 serisi debi olarak uygun ama PTFE diyafram 'talep üzerine' — teyit edilecek. NMP830 KTDC-B'de PTFE+FFKM standart ama debisi 2100 sccm, yani hedefin 10 katı; son çare olarak devri kısılıp MFC ile kontrol edilerek kullanılabilir.</t>
+          <t>ŞARTNAME: 150–300 sccm çalışma debisi, sızdırmaz (kapalı döngü), fırçasız DC (devir ayarlı), ıslak malzeme FKM (Viton) veya daha iyisi — NBR ve EPDM OLMAZ, organikleri emip geri salar. PTFE kaplı diyafram ideal ama şart değil; PTFE ısrarı bizi 2000 sccm'lik pompalara zorluyor, debi uyumu malzemeden daha önemli çünkü ölçümümüz kesim öncesi/sonrası farkı. ADAYLAR: Parker Hannifin T5/T2 serisi (Li 2019 bitki VOC örneklemesinde T5-1IC-03-1EEP'i 480 sccm'de kullanmış — literatür örneği var), Schwarzer Precision SP serisi, Thomas / Gardner Denver, Xavitech V serisi (devir kontrolü dahili), Boxer, TCS Micropumps. KNF de teklif versin ama tek seçenek değil. ELEME: Air Dimensions Dia-Vac — malzemesi ideal ama en küçüğü 13 L/dk, çok büyük.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="n">
+      <c r="A20" s="25" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>POMPA / AKIŞ</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C20" s="26" t="inlineStr">
         <is>
           <t>Alicat 200 sccm MFC</t>
         </is>
@@ -1299,15 +1305,15 @@
           <t>Döngü debi kontrol + ölçüm (ELİMİZDE VAR)</t>
         </is>
       </c>
-      <c r="E20" s="11" t="n">
+      <c r="E20" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="12" t="n"/>
-      <c r="G20" s="12">
+      <c r="F20" s="26" t="n"/>
+      <c r="G20" s="26">
         <f>IF(F20="","",E20*F20)</f>
         <v/>
       </c>
-      <c r="H20" s="12" t="inlineStr">
+      <c r="H20" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1334,15 +1340,15 @@
       <c r="I21" s="4" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="n">
+      <c r="A22" s="25" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="26" t="inlineStr">
         <is>
           <t>ODACIK</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C22" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1352,15 +1358,15 @@
           <t>PTFE hortum, 6 mm dış / 4 mm iç çap</t>
         </is>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="E22" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="F22" s="12" t="n"/>
-      <c r="G22" s="12">
+      <c r="F22" s="26" t="n"/>
+      <c r="G22" s="26">
         <f>IF(F22="","",E22*F22)</f>
         <v/>
       </c>
-      <c r="H22" s="12" t="inlineStr">
+      <c r="H22" s="26" t="inlineStr">
         <is>
           <t>Neumo / lab sarf</t>
         </is>
@@ -1372,15 +1378,15 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="n">
+      <c r="A23" s="25" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>ODACIK</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C23" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1390,15 +1396,15 @@
           <t>Cam kavanoz, 1 L borosilikat, geniş ağız, PTFE astarlı kapak</t>
         </is>
       </c>
-      <c r="E23" s="11" t="n">
+      <c r="E23" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F23" s="12" t="n"/>
-      <c r="G23" s="12">
+      <c r="F23" s="26" t="n"/>
+      <c r="G23" s="26">
         <f>IF(F23="","",E23*F23)</f>
         <v/>
       </c>
-      <c r="H23" s="12" t="inlineStr">
+      <c r="H23" s="26" t="inlineStr">
         <is>
           <t>Lab sarf</t>
         </is>
@@ -1448,15 +1454,15 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n">
+      <c r="A25" s="25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>ODACIK</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1466,15 +1472,15 @@
           <t>Silikon conta bandı, kutu kapağı için</t>
         </is>
       </c>
-      <c r="E25" s="11" t="n">
+      <c r="E25" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="12" t="n"/>
-      <c r="G25" s="12">
+      <c r="F25" s="26" t="n"/>
+      <c r="G25" s="26">
         <f>IF(F25="","",E25*F25)</f>
         <v/>
       </c>
-      <c r="H25" s="12" t="inlineStr">
+      <c r="H25" s="26" t="inlineStr">
         <is>
           <t>Hırdavat</t>
         </is>
@@ -1486,15 +1492,15 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="n">
+      <c r="A26" s="25" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="26" t="inlineStr">
         <is>
           <t>ODACIK</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C26" s="26" t="inlineStr">
         <is>
           <t>SHT31 veya muadili</t>
         </is>
@@ -1504,15 +1510,15 @@
           <t>Sıcaklık / bağıl nem sensörü, kayıtlı</t>
         </is>
       </c>
-      <c r="E26" s="11" t="n">
+      <c r="E26" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="12" t="n"/>
-      <c r="G26" s="12">
+      <c r="F26" s="26" t="n"/>
+      <c r="G26" s="26">
         <f>IF(F26="","",E26*F26)</f>
         <v/>
       </c>
-      <c r="H26" s="12" t="inlineStr">
+      <c r="H26" s="26" t="inlineStr">
         <is>
           <t>Elektronik</t>
         </is>
@@ -1524,15 +1530,15 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="n">
+      <c r="A27" s="25" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="26" t="inlineStr">
         <is>
           <t>ODACIK</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="C27" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1542,15 +1548,15 @@
           <t>Nitril eldiven + kelepçe (kutuya eldiven portu)</t>
         </is>
       </c>
-      <c r="E27" s="11" t="n">
+      <c r="E27" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="F27" s="12" t="n"/>
-      <c r="G27" s="12">
+      <c r="F27" s="26" t="n"/>
+      <c r="G27" s="26">
         <f>IF(F27="","",E27*F27)</f>
         <v/>
       </c>
-      <c r="H27" s="12" t="inlineStr">
+      <c r="H27" s="26" t="inlineStr">
         <is>
           <t>Lab sarf</t>
         </is>
@@ -1577,15 +1583,15 @@
       <c r="I28" s="4" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="n">
+      <c r="A29" s="25" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B29" s="26" t="inlineStr">
         <is>
           <t>TEST BİLEŞİĞİ</t>
         </is>
       </c>
-      <c r="C29" s="12" t="inlineStr">
+      <c r="C29" s="26" t="inlineStr">
         <is>
           <t>CAS 119-36-8</t>
         </is>
@@ -1595,15 +1601,15 @@
           <t>Metil salisilat, reaktif saflığı &gt;=%99, 100 mL</t>
         </is>
       </c>
-      <c r="E29" s="11" t="n">
+      <c r="E29" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="12" t="n"/>
-      <c r="G29" s="12">
+      <c r="F29" s="26" t="n"/>
+      <c r="G29" s="26">
         <f>IF(F29="","",E29*F29)</f>
         <v/>
       </c>
-      <c r="H29" s="12" t="inlineStr">
+      <c r="H29" s="26" t="inlineStr">
         <is>
           <t>Merck / Sigma / Isolab</t>
         </is>
@@ -1615,15 +1621,15 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="n">
+      <c r="A30" s="25" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B30" s="26" t="inlineStr">
         <is>
           <t>TEST BİLEŞİĞİ</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr">
+      <c r="C30" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1633,15 +1639,15 @@
           <t>Mikrolitre şırınga, 10 µL, gaz sızdırmaz</t>
         </is>
       </c>
-      <c r="E30" s="11" t="n">
+      <c r="E30" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F30" s="12" t="n"/>
-      <c r="G30" s="12">
+      <c r="F30" s="26" t="n"/>
+      <c r="G30" s="26">
         <f>IF(F30="","",E30*F30)</f>
         <v/>
       </c>
-      <c r="H30" s="12" t="inlineStr">
+      <c r="H30" s="26" t="inlineStr">
         <is>
           <t>Lab sarf</t>
         </is>
